--- a/DOCUMENTOS/Diccionario_de_Datos.xlsx
+++ b/DOCUMENTOS/Diccionario_de_Datos.xlsx
@@ -1,17 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\PracticaProfesional\InstitutoNET Documentación\Requerimiento16\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <bookViews>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12336"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="Hoja 1" sheetId="1" r:id="rId5"/>
+    <sheet name="Hoja 1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="263" uniqueCount="114">
   <si>
     <t>MODULO CARRERA</t>
   </si>
@@ -302,60 +310,139 @@
   </si>
   <si>
     <t>Grupo 1: Acevedo Cecilia _Mendez Selene _Visgarra Pablo _Godoy Sabrina _Ledesma Franco_Molina Matias</t>
+  </si>
+  <si>
+    <t>CarrerasCodigoBloque</t>
+  </si>
+  <si>
+    <t>varchar(20)</t>
+  </si>
+  <si>
+    <t>AniosCarrerasCodigoBloque</t>
+  </si>
+  <si>
+    <t>Codigo identificatorio para las carreras.</t>
+  </si>
+  <si>
+    <t>Codigo identificatorio para los diferentes años de una carrera.</t>
+  </si>
+  <si>
+    <t>MateriasCodigoBloque</t>
+  </si>
+  <si>
+    <t>Codigo identificatorio para saber a que carrera y año pertenecen</t>
+  </si>
+  <si>
+    <t>Identificador de la carrera a la que pertenece esta materia.</t>
+  </si>
+  <si>
+    <t>FinalPromocion</t>
+  </si>
+  <si>
+    <t>char(1)</t>
+  </si>
+  <si>
+    <t>Indica si la materia es promocional o requiere realizar un examen final.</t>
+  </si>
+  <si>
+    <t>CHECK ( F ) o ( P)</t>
+  </si>
+  <si>
+    <t>Aclaración / Observaciones</t>
+  </si>
+  <si>
+    <t>1 = Activa (Color Verde)  
+2 = Inactiva (Color Amarillo) 
+3 = Borrador (Color Rojo)</t>
+  </si>
+  <si>
+    <t>Correcciones Req 16 - Grupo 5: Fernandez Franco, Mourdad Ignacio, Campos Santiago.</t>
+  </si>
+  <si>
+    <t>CantidadCorrelativas</t>
+  </si>
+  <si>
+    <t>Cantidad de correlativas que posee la carrera.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="10">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="13">
     <font>
-      <sz val="10.0"/>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="12.0"/>
+      <sz val="12"/>
       <color theme="1"/>
       <name val="Arial"/>
     </font>
     <font>
-      <sz val="14.0"/>
+      <sz val="14"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
     </font>
     <font>
+      <sz val="10"/>
       <color rgb="FF1F1F1F"/>
       <name val="&quot;Google Sans Text&quot;"/>
     </font>
     <font>
+      <sz val="10"/>
       <color rgb="FF1F1F1F"/>
       <name val="Arial"/>
     </font>
     <font>
       <b/>
+      <sz val="10"/>
       <color rgb="FF1F1F1F"/>
       <name val="&quot;Google Sans Text&quot;"/>
     </font>
     <font>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
     </font>
     <font>
       <b/>
+      <sz val="10"/>
       <color rgb="FF1F1F1F"/>
       <name val="Google Sans Text"/>
     </font>
     <font>
+      <sz val="10"/>
       <color rgb="FF1F1F1F"/>
       <name val="Google Sans Text"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9.5"/>
+      <color rgb="FF0000FF"/>
+      <name val="Consolas"/>
+      <family val="3"/>
     </font>
   </fonts>
   <fills count="6">
@@ -363,7 +450,7 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -391,173 +478,263 @@
     </fill>
   </fills>
   <borders count="2">
-    <border/>
     <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
       <top style="thin">
         <color rgb="FF000000"/>
       </top>
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+  <cellXfs count="37">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment readingOrder="0"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="3" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="3" fontId="6" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="bottom"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="bottom"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="4" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="5" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="bottom"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="bottom"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="4" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="4" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="4" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="4" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="bottom"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="4">
+  <dxfs count="14">
     <dxf>
-      <font/>
       <fill>
-        <patternFill patternType="none"/>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF3F3F3"/>
+          <bgColor rgb="FFF3F3F3"/>
+        </patternFill>
       </fill>
-      <border/>
     </dxf>
     <dxf>
-      <font/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF3F3F3"/>
+          <bgColor rgb="FFF3F3F3"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="FF38761D"/>
           <bgColor rgb="FF38761D"/>
         </patternFill>
       </fill>
-      <border/>
     </dxf>
     <dxf>
-      <font/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF3F3F3"/>
+          <bgColor rgb="FFF3F3F3"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="FFFFFFFF"/>
           <bgColor rgb="FFFFFFFF"/>
         </patternFill>
       </fill>
-      <border/>
     </dxf>
     <dxf>
-      <font/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF38761D"/>
+          <bgColor rgb="FF38761D"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="FFF3F3F3"/>
           <bgColor rgb="FFF3F3F3"/>
         </patternFill>
       </fill>
-      <border/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF38761D"/>
+          <bgColor rgb="FF38761D"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF3F3F3"/>
+          <bgColor rgb="FFF3F3F3"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF38761D"/>
+          <bgColor rgb="FF38761D"/>
+        </patternFill>
+      </fill>
     </dxf>
   </dxfs>
   <tableStyles count="5">
-    <tableStyle count="3" pivot="0" name="Hoja 1-style">
-      <tableStyleElement dxfId="1" type="headerRow"/>
-      <tableStyleElement dxfId="2" type="firstRowStripe"/>
-      <tableStyleElement dxfId="3" type="secondRowStripe"/>
+    <tableStyle name="Hoja 1-style" pivot="0" count="3">
+      <tableStyleElement type="headerRow" dxfId="13"/>
+      <tableStyleElement type="firstRowStripe" dxfId="12"/>
+      <tableStyleElement type="secondRowStripe" dxfId="11"/>
     </tableStyle>
-    <tableStyle count="3" pivot="0" name="Hoja 1-style 2">
-      <tableStyleElement dxfId="1" type="headerRow"/>
-      <tableStyleElement dxfId="2" type="firstRowStripe"/>
-      <tableStyleElement dxfId="3" type="secondRowStripe"/>
+    <tableStyle name="Hoja 1-style 2" pivot="0" count="3">
+      <tableStyleElement type="headerRow" dxfId="10"/>
+      <tableStyleElement type="firstRowStripe" dxfId="9"/>
+      <tableStyleElement type="secondRowStripe" dxfId="8"/>
     </tableStyle>
-    <tableStyle count="3" pivot="0" name="Hoja 1-style 3">
-      <tableStyleElement dxfId="1" type="headerRow"/>
-      <tableStyleElement dxfId="2" type="firstRowStripe"/>
-      <tableStyleElement dxfId="3" type="secondRowStripe"/>
+    <tableStyle name="Hoja 1-style 3" pivot="0" count="3">
+      <tableStyleElement type="headerRow" dxfId="7"/>
+      <tableStyleElement type="firstRowStripe" dxfId="6"/>
+      <tableStyleElement type="secondRowStripe" dxfId="5"/>
     </tableStyle>
-    <tableStyle count="3" pivot="0" name="Hoja 1-style 4">
-      <tableStyleElement dxfId="1" type="headerRow"/>
-      <tableStyleElement dxfId="2" type="firstRowStripe"/>
-      <tableStyleElement dxfId="3" type="secondRowStripe"/>
+    <tableStyle name="Hoja 1-style 4" pivot="0" count="3">
+      <tableStyleElement type="headerRow" dxfId="4"/>
+      <tableStyleElement type="firstRowStripe" dxfId="3"/>
+      <tableStyleElement type="secondRowStripe" dxfId="2"/>
     </tableStyle>
-    <tableStyle count="2" pivot="0" name="Hoja 1-style 5">
-      <tableStyleElement dxfId="2" type="firstRowStripe"/>
-      <tableStyleElement dxfId="3" type="secondRowStripe"/>
+    <tableStyle name="Hoja 1-style 5" pivot="0" count="2">
+      <tableStyleElement type="firstRowStripe" dxfId="1"/>
+      <tableStyleElement type="secondRowStripe" dxfId="0"/>
     </tableStyle>
   </tableStyles>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
 </file>
 
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
@@ -565,99 +742,86 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="B3:M19" displayName="Table_1" name="Table_1" id="1">
-  <tableColumns count="12">
-    <tableColumn name="Column1" id="1"/>
-    <tableColumn name="Column2" id="2"/>
-    <tableColumn name="Column3" id="3"/>
-    <tableColumn name="Column4" id="4"/>
-    <tableColumn name="Column5" id="5"/>
-    <tableColumn name="Column6" id="6"/>
-    <tableColumn name="Column7" id="7"/>
-    <tableColumn name="Column8" id="8"/>
-    <tableColumn name="Column9" id="9"/>
-    <tableColumn name="Column10" id="10"/>
-    <tableColumn name="Column11" id="11"/>
-    <tableColumn name="Column12" id="12"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table_1" displayName="Table_1" ref="B3:H22" headerRowCount="0">
+  <tableColumns count="7">
+    <tableColumn id="1" name="Column1"/>
+    <tableColumn id="2" name="Column2"/>
+    <tableColumn id="3" name="Column3"/>
+    <tableColumn id="4" name="Column4"/>
+    <tableColumn id="5" name="Column5"/>
+    <tableColumn id="6" name="Column6"/>
+    <tableColumn id="7" name="Columna1"/>
   </tableColumns>
-  <tableStyleInfo name="Hoja 1-style" showColumnStripes="0" showFirstColumn="1" showLastColumn="1" showRowStripes="1"/>
-  <extLst>
-    <ext uri="GoogleSheetsCustomDataVersion1">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" headerRowCount="1"/>
-    </ext>
-  </extLst>
+  <tableStyleInfo name="Hoja 1-style" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="B24:M29" displayName="Table_2" name="Table_2" id="2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table_2" displayName="Table_2" ref="B25:M31" headerRowCount="0">
   <tableColumns count="12">
-    <tableColumn name="Column1" id="1"/>
-    <tableColumn name="Column2" id="2"/>
-    <tableColumn name="Column3" id="3"/>
-    <tableColumn name="Column4" id="4"/>
-    <tableColumn name="Column5" id="5"/>
-    <tableColumn name="Column6" id="6"/>
-    <tableColumn name="Column7" id="7"/>
-    <tableColumn name="Column8" id="8"/>
-    <tableColumn name="Column9" id="9"/>
-    <tableColumn name="Column10" id="10"/>
-    <tableColumn name="Column11" id="11"/>
-    <tableColumn name="Column12" id="12"/>
+    <tableColumn id="1" name="Column1"/>
+    <tableColumn id="2" name="Column2"/>
+    <tableColumn id="3" name="Column3"/>
+    <tableColumn id="4" name="Column4"/>
+    <tableColumn id="5" name="Column5"/>
+    <tableColumn id="6" name="Column6"/>
+    <tableColumn id="7" name="Column7"/>
+    <tableColumn id="8" name="Column8"/>
+    <tableColumn id="9" name="Column9"/>
+    <tableColumn id="10" name="Column10"/>
+    <tableColumn id="11" name="Column11"/>
+    <tableColumn id="12" name="Column12"/>
   </tableColumns>
-  <tableStyleInfo name="Hoja 1-style 2" showColumnStripes="0" showFirstColumn="1" showLastColumn="1" showRowStripes="1"/>
-  <extLst>
-    <ext uri="GoogleSheetsCustomDataVersion1">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" headerRowCount="1"/>
-    </ext>
-  </extLst>
+  <tableStyleInfo name="Hoja 1-style 2" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="B34:G43" displayName="Table_3" name="Table_3" id="3">
-  <tableColumns count="6">
-    <tableColumn name="Tabla" id="1"/>
-    <tableColumn name="Campo" id="2"/>
-    <tableColumn name="Tipo" id="3"/>
-    <tableColumn name="Descripción" id="4"/>
-    <tableColumn name="Clave" id="5"/>
-    <tableColumn name="Regla" id="6"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table_3" displayName="Table_3" ref="B37:H48">
+  <tableColumns count="7">
+    <tableColumn id="1" name="Tabla"/>
+    <tableColumn id="2" name="Campo"/>
+    <tableColumn id="3" name="Tipo"/>
+    <tableColumn id="4" name="Descripción"/>
+    <tableColumn id="5" name="Clave"/>
+    <tableColumn id="6" name="Regla"/>
+    <tableColumn id="7" name="Aclaración / Observaciones"/>
   </tableColumns>
-  <tableStyleInfo name="Hoja 1-style 3" showColumnStripes="0" showFirstColumn="1" showLastColumn="1" showRowStripes="1"/>
+  <tableStyleInfo name="Hoja 1-style 3" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="B47:G50" displayName="Table_4" name="Table_4" id="4">
-  <tableColumns count="6">
-    <tableColumn name="Tabla" id="1"/>
-    <tableColumn name="Campo" id="2"/>
-    <tableColumn name="Tipo" id="3"/>
-    <tableColumn name="Descripción" id="4"/>
-    <tableColumn name="Clave" id="5"/>
-    <tableColumn name="Regla" id="6"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Table_4" displayName="Table_4" ref="B53:H56">
+  <tableColumns count="7">
+    <tableColumn id="1" name="Tabla"/>
+    <tableColumn id="2" name="Campo"/>
+    <tableColumn id="3" name="Tipo"/>
+    <tableColumn id="4" name="Descripción"/>
+    <tableColumn id="5" name="Clave"/>
+    <tableColumn id="6" name="Regla"/>
+    <tableColumn id="7" name="Aclaración / Observaciones"/>
   </tableColumns>
-  <tableStyleInfo name="Hoja 1-style 4" showColumnStripes="0" showFirstColumn="1" showLastColumn="1" showRowStripes="1"/>
+  <tableStyleInfo name="Hoja 1-style 4" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="B54:G56" displayName="Table_5" name="Table_5" id="5">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="Table_5" displayName="Table_5" ref="B64:G67" headerRowCount="0">
   <tableColumns count="6">
-    <tableColumn name="Column1" id="1"/>
-    <tableColumn name="Column2" id="2"/>
-    <tableColumn name="Column3" id="3"/>
-    <tableColumn name="Column4" id="4"/>
-    <tableColumn name="Column5" id="5"/>
-    <tableColumn name="Column6" id="6"/>
+    <tableColumn id="1" name="Column1"/>
+    <tableColumn id="2" name="Column2"/>
+    <tableColumn id="3" name="Column3"/>
+    <tableColumn id="4" name="Column4"/>
+    <tableColumn id="5" name="Column5"/>
+    <tableColumn id="6" name="Column6"/>
   </tableColumns>
-  <tableStyleInfo name="Hoja 1-style 5" showColumnStripes="0" showFirstColumn="1" showLastColumn="1" showRowStripes="1"/>
+  <tableStyleInfo name="Hoja 1-style 5" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -847,1137 +1011,1137 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A2:N79"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.5546875" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
-    <col customWidth="1" min="3" max="3" width="20.5"/>
-    <col customWidth="1" min="5" max="5" width="39.0"/>
-    <col customWidth="1" min="7" max="7" width="25.5"/>
-    <col customWidth="1" min="8" max="8" width="7.5"/>
-    <col customWidth="1" min="9" max="9" width="4.25"/>
-    <col customWidth="1" min="10" max="10" width="3.63"/>
-    <col customWidth="1" min="11" max="11" width="7.5"/>
-    <col customWidth="1" min="12" max="12" width="20.5"/>
-    <col customWidth="1" min="14" max="14" width="36.38"/>
+    <col min="3" max="3" width="24.88671875" customWidth="1"/>
+    <col min="5" max="5" width="47.88671875" customWidth="1"/>
+    <col min="7" max="7" width="25.44140625" customWidth="1"/>
+    <col min="8" max="8" width="36.44140625" customWidth="1"/>
+    <col min="9" max="9" width="4.33203125" customWidth="1"/>
+    <col min="10" max="10" width="3.5546875" customWidth="1"/>
+    <col min="11" max="11" width="7.44140625" customWidth="1"/>
+    <col min="12" max="12" width="20.44140625" customWidth="1"/>
+    <col min="14" max="14" width="36.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2">
-      <c r="B2" s="1" t="s">
+    <row r="2" spans="2:8" ht="15.75" customHeight="1">
+      <c r="B2" s="34" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="3">
-      <c r="B3" s="2" t="s">
+      <c r="C2" s="35"/>
+      <c r="D2" s="35"/>
+      <c r="E2" s="35"/>
+      <c r="F2" s="35"/>
+      <c r="G2" s="35"/>
+    </row>
+    <row r="3" spans="2:8" ht="15.75" customHeight="1">
+      <c r="B3" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="E3" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="F3" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="G3" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H3" s="3"/>
-      <c r="I3" s="3"/>
-      <c r="J3" s="3"/>
-      <c r="K3" s="3"/>
-      <c r="L3" s="3"/>
-      <c r="M3" s="3"/>
-    </row>
-    <row r="4">
-      <c r="B4" s="4" t="s">
+      <c r="H3" s="1" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="4" spans="2:8" ht="26.4">
+      <c r="B4" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C4" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="D4" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="E4" s="4" t="s">
+      <c r="E4" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F4" s="5" t="s">
+      <c r="F4" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="G4" s="4" t="s">
+      <c r="G4" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="H4" s="3"/>
-      <c r="I4" s="6"/>
-      <c r="J4" s="3"/>
-      <c r="K4" s="3"/>
-      <c r="L4" s="3"/>
-      <c r="M4" s="3"/>
-    </row>
-    <row r="5">
-      <c r="B5" s="4" t="s">
+    </row>
+    <row r="5" spans="2:8" ht="13.2">
+      <c r="B5" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="C5" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="D5" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="E5" s="4" t="s">
+      <c r="E5" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="F5" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="G5" s="4" t="s">
+      <c r="F5" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="G5" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="H5" s="3"/>
-      <c r="I5" s="6"/>
-      <c r="J5" s="3"/>
-      <c r="K5" s="3"/>
-      <c r="L5" s="3"/>
-      <c r="M5" s="3"/>
-    </row>
-    <row r="6">
-      <c r="B6" s="4" t="s">
+    </row>
+    <row r="6" spans="2:8" ht="13.2">
+      <c r="B6" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="C6" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="D6" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="E6" s="4" t="s">
+      <c r="E6" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="F6" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="G6" s="4" t="s">
+      <c r="F6" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="G6" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="H6" s="3"/>
-      <c r="I6" s="6"/>
-      <c r="J6" s="3"/>
-      <c r="K6" s="3"/>
-      <c r="L6" s="3"/>
-      <c r="M6" s="3"/>
-    </row>
-    <row r="7">
-      <c r="B7" s="4" t="s">
+    </row>
+    <row r="7" spans="2:8" ht="26.4">
+      <c r="B7" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="C7" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="D7" s="7" t="s">
+      <c r="D7" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="E7" s="4" t="s">
+      <c r="E7" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="F7" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="G7" s="4" t="s">
+      <c r="F7" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="G7" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="H7" s="3"/>
-      <c r="I7" s="6"/>
-      <c r="J7" s="3"/>
-      <c r="K7" s="3"/>
-      <c r="L7" s="3"/>
-      <c r="M7" s="3"/>
-    </row>
-    <row r="8">
-      <c r="B8" s="4" t="s">
+    </row>
+    <row r="8" spans="2:8" ht="26.4">
+      <c r="B8" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="C8" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="D8" s="4" t="s">
+      <c r="D8" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="E8" s="4" t="s">
+      <c r="E8" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="F8" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="G8" s="4" t="s">
+      <c r="F8" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="G8" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="H8" s="3"/>
-      <c r="I8" s="6"/>
-      <c r="J8" s="3"/>
-      <c r="K8" s="3"/>
-      <c r="L8" s="3"/>
-      <c r="M8" s="3"/>
-    </row>
-    <row r="9">
-      <c r="B9" s="4" t="s">
+    </row>
+    <row r="9" spans="2:8" ht="26.4">
+      <c r="B9" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="C9" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="D9" s="4" t="s">
+      <c r="D9" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="E9" s="4" t="s">
+      <c r="E9" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="F9" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="G9" s="4" t="s">
+      <c r="F9" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="G9" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="H9" s="3"/>
-      <c r="I9" s="6"/>
-      <c r="J9" s="3"/>
-      <c r="K9" s="3"/>
-      <c r="L9" s="3"/>
-      <c r="M9" s="3"/>
-    </row>
-    <row r="10">
-      <c r="B10" s="4" t="s">
+    </row>
+    <row r="10" spans="2:8" ht="26.4">
+      <c r="B10" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C10" s="4" t="s">
+      <c r="C10" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="D10" s="4" t="s">
+      <c r="D10" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="E10" s="4" t="s">
+      <c r="E10" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="F10" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="G10" s="4" t="s">
+      <c r="F10" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="G10" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="H10" s="3"/>
-      <c r="I10" s="6"/>
-      <c r="J10" s="3"/>
-      <c r="K10" s="3"/>
-      <c r="L10" s="3"/>
-      <c r="M10" s="3"/>
-    </row>
-    <row r="11">
-      <c r="B11" s="4" t="s">
+    </row>
+    <row r="11" spans="2:8" ht="13.2">
+      <c r="B11" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C11" s="4" t="s">
+      <c r="C11" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="D11" s="4" t="s">
+      <c r="D11" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="E11" s="4" t="s">
+      <c r="E11" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="F11" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="G11" s="4" t="s">
+      <c r="F11" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="G11" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="H11" s="3"/>
-      <c r="I11" s="6"/>
-      <c r="J11" s="3"/>
-      <c r="K11" s="3"/>
-      <c r="L11" s="3"/>
-      <c r="M11" s="3"/>
-    </row>
-    <row r="12">
-      <c r="B12" s="4" t="s">
+    </row>
+    <row r="12" spans="2:8" ht="26.4">
+      <c r="B12" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C12" s="4" t="s">
+      <c r="C12" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="D12" s="4" t="s">
+      <c r="D12" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="E12" s="4" t="s">
+      <c r="E12" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="F12" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="G12" s="4" t="s">
+      <c r="F12" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="G12" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="H12" s="3"/>
-      <c r="I12" s="6"/>
-      <c r="J12" s="3"/>
-      <c r="K12" s="3"/>
-      <c r="L12" s="3"/>
-      <c r="M12" s="3"/>
-    </row>
-    <row r="13">
-      <c r="B13" s="4" t="s">
+    </row>
+    <row r="13" spans="2:8" ht="13.2">
+      <c r="B13" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C13" s="4" t="s">
+      <c r="C13" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="D13" s="4" t="s">
+      <c r="D13" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="E13" s="4" t="s">
+      <c r="E13" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="F13" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="G13" s="4" t="s">
+      <c r="F13" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="G13" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="H13" s="3"/>
-      <c r="I13" s="6"/>
-      <c r="J13" s="3"/>
-      <c r="K13" s="3"/>
-      <c r="L13" s="3"/>
-      <c r="M13" s="3"/>
-    </row>
-    <row r="14">
-      <c r="B14" s="4" t="s">
+    </row>
+    <row r="14" spans="2:8" ht="26.4">
+      <c r="B14" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C14" s="4" t="s">
+      <c r="C14" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="D14" s="4" t="s">
+      <c r="D14" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="E14" s="4" t="s">
+      <c r="E14" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="F14" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="G14" s="4" t="s">
+      <c r="F14" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="G14" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="H14" s="8"/>
-      <c r="I14" s="8"/>
-      <c r="J14" s="8"/>
-      <c r="K14" s="8"/>
-      <c r="L14" s="8"/>
-      <c r="M14" s="8"/>
-    </row>
-    <row r="15">
-      <c r="B15" s="4" t="s">
+    </row>
+    <row r="15" spans="2:8" ht="32.25" customHeight="1">
+      <c r="B15" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C15" s="4" t="s">
+      <c r="C15" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="D15" s="4" t="s">
+      <c r="D15" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="E15" s="4" t="s">
+      <c r="E15" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="F15" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="G15" s="4" t="s">
+      <c r="F15" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="G15" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="H15" s="8"/>
-      <c r="I15" s="8"/>
-      <c r="J15" s="8"/>
-      <c r="K15" s="8"/>
-      <c r="L15" s="8"/>
-      <c r="M15" s="8"/>
-    </row>
-    <row r="16">
-      <c r="B16" s="4" t="s">
+    </row>
+    <row r="16" spans="2:8" ht="13.2">
+      <c r="B16" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C16" s="4" t="s">
+      <c r="C16" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="D16" s="4" t="s">
+      <c r="D16" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="E16" s="4" t="s">
+      <c r="E16" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="F16" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="G16" s="4" t="s">
+      <c r="F16" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="G16" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="H16" s="8"/>
-      <c r="I16" s="8"/>
-      <c r="J16" s="8"/>
-      <c r="K16" s="8"/>
-      <c r="L16" s="8"/>
-      <c r="M16" s="8"/>
-    </row>
-    <row r="17">
-      <c r="B17" s="4" t="s">
+    </row>
+    <row r="17" spans="2:14" ht="13.2">
+      <c r="B17" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C17" s="4" t="s">
+      <c r="C17" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="D17" s="4" t="s">
+      <c r="D17" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="E17" s="4" t="s">
+      <c r="E17" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="F17" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="G17" s="4" t="s">
+      <c r="F17" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="G17" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="H17" s="8"/>
-      <c r="I17" s="8"/>
-      <c r="J17" s="8"/>
-      <c r="K17" s="8"/>
-      <c r="L17" s="8"/>
-      <c r="M17" s="8"/>
-    </row>
-    <row r="18">
-      <c r="B18" s="4" t="s">
+    </row>
+    <row r="18" spans="2:14" ht="26.4">
+      <c r="B18" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C18" s="4" t="s">
+      <c r="C18" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="D18" s="4" t="s">
+      <c r="D18" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="E18" s="4" t="s">
+      <c r="E18" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="F18" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="G18" s="4" t="s">
+      <c r="F18" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="G18" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="H18" s="8"/>
-      <c r="I18" s="8"/>
-      <c r="J18" s="8"/>
-      <c r="K18" s="8"/>
-      <c r="L18" s="8"/>
-      <c r="M18" s="8"/>
-    </row>
-    <row r="19">
-      <c r="B19" s="4" t="s">
+    </row>
+    <row r="19" spans="2:14" ht="44.25" customHeight="1">
+      <c r="B19" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C19" s="4" t="s">
+      <c r="C19" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="D19" s="4" t="s">
+      <c r="D19" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="E19" s="4" t="s">
+      <c r="E19" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="F19" s="5" t="s">
+      <c r="F19" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="G19" s="4" t="s">
+      <c r="G19" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="H19" s="8"/>
-      <c r="I19" s="8"/>
-      <c r="J19" s="8"/>
-      <c r="K19" s="8"/>
-      <c r="L19" s="8"/>
-      <c r="M19" s="8"/>
-    </row>
-    <row r="23">
-      <c r="B23" s="1" t="s">
+      <c r="H19" s="32" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="20" spans="2:14" ht="39" customHeight="1">
+      <c r="B20" s="22" t="s">
+        <v>7</v>
+      </c>
+      <c r="C20" s="22" t="s">
+        <v>97</v>
+      </c>
+      <c r="D20" s="22" t="s">
+        <v>98</v>
+      </c>
+      <c r="E20" s="24" t="s">
+        <v>100</v>
+      </c>
+      <c r="F20" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="G20" s="23" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="21" spans="2:14" ht="15.75" customHeight="1">
+      <c r="B21" t="s">
+        <v>7</v>
+      </c>
+      <c r="C21" s="33" t="s">
+        <v>112</v>
+      </c>
+      <c r="D21" t="s">
+        <v>9</v>
+      </c>
+      <c r="E21" t="s">
+        <v>113</v>
+      </c>
+      <c r="G21" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="22" spans="2:14" ht="15.75" customHeight="1">
+      <c r="F22" s="13" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="24" spans="2:14" ht="15.75" customHeight="1">
+      <c r="B24" s="34" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="24">
-      <c r="B24" s="2" t="s">
+      <c r="C24" s="35"/>
+      <c r="D24" s="35"/>
+      <c r="E24" s="35"/>
+      <c r="F24" s="35"/>
+      <c r="G24" s="35"/>
+    </row>
+    <row r="25" spans="2:14" ht="18" customHeight="1">
+      <c r="B25" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C24" s="2" t="s">
+      <c r="C25" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D24" s="2" t="s">
+      <c r="D25" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E24" s="2" t="s">
+      <c r="E25" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F24" s="2" t="s">
+      <c r="F25" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G24" s="2" t="s">
+      <c r="G25" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H24" s="3"/>
-      <c r="I24" s="3"/>
-      <c r="J24" s="3"/>
-      <c r="K24" s="3"/>
-      <c r="L24" s="3"/>
-      <c r="M24" s="3"/>
-      <c r="N24" s="9"/>
-    </row>
-    <row r="25">
-      <c r="B25" s="10" t="s">
+      <c r="H25" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="I25" s="2"/>
+      <c r="J25" s="2"/>
+      <c r="K25" s="2"/>
+      <c r="L25" s="2"/>
+      <c r="M25" s="2"/>
+      <c r="N25" s="7"/>
+    </row>
+    <row r="26" spans="2:14" ht="26.4">
+      <c r="B26" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="C25" s="10" t="s">
+      <c r="C26" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="D25" s="10" t="s">
+      <c r="D26" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="E25" s="10" t="s">
+      <c r="E26" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="F25" s="11" t="s">
+      <c r="F26" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="G25" s="4" t="s">
+      <c r="G26" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="H25" s="3"/>
-      <c r="I25" s="6"/>
-      <c r="J25" s="3"/>
-      <c r="K25" s="3"/>
-      <c r="L25" s="3"/>
-      <c r="M25" s="3"/>
-      <c r="N25" s="9"/>
-    </row>
-    <row r="26">
-      <c r="B26" s="10" t="s">
+      <c r="H26" s="12"/>
+      <c r="I26" s="5"/>
+      <c r="J26" s="2"/>
+      <c r="K26" s="2"/>
+      <c r="L26" s="2"/>
+      <c r="M26" s="2"/>
+      <c r="N26" s="7"/>
+    </row>
+    <row r="27" spans="2:14" ht="26.4">
+      <c r="B27" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="C26" s="10" t="s">
+      <c r="C27" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="D26" s="10" t="s">
+      <c r="D27" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="E26" s="10" t="s">
+      <c r="E27" s="8" t="s">
         <v>59</v>
       </c>
-      <c r="F26" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="G26" s="10" t="s">
+      <c r="F27" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="G27" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="H26" s="3"/>
-      <c r="I26" s="6"/>
-      <c r="J26" s="3"/>
-      <c r="K26" s="3"/>
-      <c r="L26" s="3"/>
-      <c r="M26" s="3"/>
-      <c r="N26" s="9"/>
-    </row>
-    <row r="27">
-      <c r="B27" s="10" t="s">
+      <c r="H27" s="12"/>
+      <c r="I27" s="5"/>
+      <c r="J27" s="2"/>
+      <c r="K27" s="2"/>
+      <c r="L27" s="2"/>
+      <c r="M27" s="2"/>
+      <c r="N27" s="7"/>
+    </row>
+    <row r="28" spans="2:14" ht="26.4">
+      <c r="B28" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="C27" s="4" t="s">
+      <c r="C28" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="D27" s="4" t="s">
+      <c r="D28" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="E27" s="4" t="s">
+      <c r="E28" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="F27" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="G27" s="4" t="s">
+      <c r="F28" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="G28" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="H27" s="3"/>
-      <c r="I27" s="6"/>
-      <c r="J27" s="3"/>
-      <c r="K27" s="3"/>
-      <c r="L27" s="3"/>
-      <c r="M27" s="3"/>
-      <c r="N27" s="9"/>
-    </row>
-    <row r="28">
-      <c r="B28" s="10" t="s">
+      <c r="H28" s="12"/>
+      <c r="I28" s="5"/>
+      <c r="J28" s="2"/>
+      <c r="K28" s="2"/>
+      <c r="L28" s="2"/>
+      <c r="M28" s="2"/>
+      <c r="N28" s="7"/>
+    </row>
+    <row r="29" spans="2:14" ht="26.4">
+      <c r="B29" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="C28" s="4" t="s">
+      <c r="C29" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="D28" s="4" t="s">
+      <c r="D29" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="E28" s="4" t="s">
+      <c r="E29" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="F28" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="G28" s="7" t="s">
+      <c r="F29" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="G29" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="H28" s="3"/>
-      <c r="I28" s="6"/>
-      <c r="J28" s="3"/>
-      <c r="K28" s="3"/>
-      <c r="L28" s="3"/>
-      <c r="M28" s="3"/>
-      <c r="N28" s="9"/>
-    </row>
-    <row r="29">
-      <c r="B29" s="10" t="s">
+      <c r="H29" s="6"/>
+      <c r="I29" s="5"/>
+      <c r="J29" s="2"/>
+      <c r="K29" s="2"/>
+      <c r="L29" s="2"/>
+      <c r="M29" s="2"/>
+      <c r="N29" s="7"/>
+    </row>
+    <row r="30" spans="2:14" ht="26.4">
+      <c r="B30" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="C29" s="10" t="s">
+      <c r="C30" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="D29" s="10" t="s">
+      <c r="D30" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="E29" s="10" t="s">
+      <c r="E30" s="29" t="s">
         <v>66</v>
       </c>
-      <c r="F29" s="11" t="s">
+      <c r="F30" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="G29" s="10" t="s">
+      <c r="G30" s="8" t="s">
         <v>67</v>
       </c>
-      <c r="H29" s="3"/>
-      <c r="I29" s="6"/>
-      <c r="J29" s="3"/>
-      <c r="K29" s="3"/>
-      <c r="L29" s="3"/>
-      <c r="M29" s="3"/>
-      <c r="N29" s="9"/>
-    </row>
-    <row r="30">
-      <c r="B30" s="12"/>
-      <c r="C30" s="7"/>
-      <c r="D30" s="7"/>
-      <c r="E30" s="7"/>
-      <c r="F30" s="7"/>
-      <c r="G30" s="7"/>
-    </row>
-    <row r="31">
-      <c r="B31" s="12"/>
-      <c r="C31" s="7"/>
-      <c r="D31" s="7"/>
-      <c r="E31" s="7"/>
-      <c r="F31" s="7"/>
-      <c r="G31" s="7"/>
-    </row>
-    <row r="32">
-      <c r="B32" s="12"/>
-      <c r="C32" s="7"/>
-      <c r="D32" s="7"/>
-      <c r="E32" s="7"/>
-      <c r="F32" s="7"/>
-      <c r="G32" s="7"/>
-    </row>
-    <row r="33">
-      <c r="B33" s="1" t="s">
+      <c r="H30" s="12"/>
+      <c r="I30" s="5"/>
+      <c r="J30" s="2"/>
+      <c r="K30" s="2"/>
+      <c r="L30" s="2"/>
+      <c r="M30" s="2"/>
+      <c r="N30" s="7"/>
+    </row>
+    <row r="31" spans="2:14" s="22" customFormat="1" ht="24" customHeight="1">
+      <c r="B31" s="25" t="s">
+        <v>55</v>
+      </c>
+      <c r="C31" s="25" t="s">
+        <v>99</v>
+      </c>
+      <c r="D31" s="25" t="s">
+        <v>98</v>
+      </c>
+      <c r="E31" s="26" t="s">
+        <v>101</v>
+      </c>
+      <c r="F31" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="G31" s="25" t="s">
+        <v>23</v>
+      </c>
+      <c r="H31" s="25"/>
+    </row>
+    <row r="32" spans="2:14" ht="13.2"/>
+    <row r="35" spans="1:12" ht="13.2">
+      <c r="A35" s="11"/>
+    </row>
+    <row r="36" spans="1:12" ht="13.8">
+      <c r="A36" s="11"/>
+      <c r="B36" s="34" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="34">
-      <c r="B34" s="2" t="s">
+      <c r="C36" s="35"/>
+      <c r="D36" s="35"/>
+      <c r="E36" s="35"/>
+      <c r="F36" s="35"/>
+      <c r="G36" s="35"/>
+    </row>
+    <row r="37" spans="1:12" ht="17.399999999999999">
+      <c r="A37" s="11"/>
+      <c r="B37" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C34" s="2" t="s">
+      <c r="C37" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D34" s="2" t="s">
+      <c r="D37" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E34" s="2" t="s">
+      <c r="E37" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F34" s="2" t="s">
+      <c r="F37" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G34" s="2" t="s">
+      <c r="G37" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="I34" s="7"/>
-      <c r="J34" s="7"/>
-      <c r="K34" s="7"/>
-      <c r="L34" s="7"/>
-      <c r="M34" s="7"/>
-      <c r="N34" s="7"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="13"/>
-      <c r="B35" s="14" t="s">
+      <c r="H37" s="1" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="38" spans="1:12" ht="26.4">
+      <c r="A38" s="11"/>
+      <c r="B38" s="12" t="s">
         <v>68</v>
       </c>
-      <c r="C35" s="14" t="s">
+      <c r="C38" s="12" t="s">
         <v>69</v>
       </c>
-      <c r="D35" s="14" t="s">
+      <c r="D38" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="E35" s="14" t="s">
+      <c r="E38" s="12" t="s">
         <v>70</v>
       </c>
-      <c r="F35" s="15" t="s">
+      <c r="F38" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="G35" s="4" t="s">
+      <c r="G38" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="I35" s="7"/>
-      <c r="J35" s="12"/>
-      <c r="K35" s="7"/>
-      <c r="L35" s="7"/>
-      <c r="M35" s="7"/>
-      <c r="N35" s="7"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="13"/>
-      <c r="B36" s="14" t="s">
+    </row>
+    <row r="39" spans="1:12" ht="13.2">
+      <c r="A39" s="11"/>
+      <c r="B39" s="12" t="s">
         <v>68</v>
       </c>
-      <c r="C36" s="14" t="s">
+      <c r="C39" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="D36" s="4" t="s">
+      <c r="D39" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="E36" s="14" t="s">
+      <c r="E39" s="12" t="s">
         <v>72</v>
       </c>
-      <c r="F36" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="G36" s="14" t="s">
+      <c r="F39" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="G39" s="12" t="s">
         <v>73</v>
       </c>
-      <c r="I36" s="7"/>
-      <c r="J36" s="12"/>
-      <c r="K36" s="7"/>
-      <c r="L36" s="7"/>
-      <c r="M36" s="7"/>
-      <c r="N36" s="7"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="13"/>
-      <c r="B37" s="14" t="s">
+    </row>
+    <row r="40" spans="1:12" ht="13.2">
+      <c r="A40" s="11"/>
+      <c r="B40" s="12" t="s">
         <v>68</v>
       </c>
-      <c r="C37" s="14" t="s">
+      <c r="C40" s="12" t="s">
         <v>56</v>
       </c>
-      <c r="D37" s="14" t="s">
+      <c r="D40" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="E37" s="14" t="s">
+      <c r="E40" s="12" t="s">
         <v>74</v>
       </c>
-      <c r="F37" s="15" t="s">
+      <c r="F40" s="13" t="s">
         <v>53</v>
       </c>
-      <c r="G37" s="14" t="s">
+      <c r="G40" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="I37" s="7"/>
-      <c r="J37" s="12"/>
-      <c r="K37" s="7"/>
-      <c r="L37" s="7"/>
-      <c r="M37" s="7"/>
-      <c r="N37" s="7"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="13"/>
-      <c r="B38" s="14" t="s">
+    </row>
+    <row r="41" spans="1:12" ht="13.2">
+      <c r="A41" s="11"/>
+      <c r="B41" s="12" t="s">
         <v>68</v>
       </c>
-      <c r="C38" s="4" t="s">
+      <c r="C41" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="D38" s="4" t="s">
+      <c r="D41" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="E38" s="4" t="s">
+      <c r="E41" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="F38" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="G38" s="4" t="s">
+      <c r="F41" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="G41" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="I38" s="7"/>
-      <c r="J38" s="12"/>
-      <c r="K38" s="7"/>
-      <c r="L38" s="7"/>
-      <c r="M38" s="7"/>
-      <c r="N38" s="7"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="13"/>
-      <c r="B39" s="14" t="s">
+    </row>
+    <row r="42" spans="1:12" ht="26.4">
+      <c r="A42" s="11"/>
+      <c r="B42" s="12" t="s">
         <v>68</v>
       </c>
-      <c r="C39" s="4" t="s">
+      <c r="C42" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="D39" s="4" t="s">
+      <c r="D42" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="E39" s="4" t="s">
+      <c r="E42" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="F39" s="5" t="s">
+      <c r="F42" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="G39" s="4" t="s">
+      <c r="G42" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="I39" s="7"/>
-      <c r="J39" s="12"/>
-      <c r="K39" s="7"/>
-      <c r="L39" s="7"/>
-      <c r="M39" s="7"/>
-      <c r="N39" s="7"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="13"/>
-      <c r="B40" s="14" t="s">
+    </row>
+    <row r="43" spans="1:12" ht="38.25" customHeight="1">
+      <c r="B43" s="12" t="s">
         <v>68</v>
       </c>
-      <c r="C40" s="14" t="s">
+      <c r="C43" s="12" t="s">
         <v>81</v>
       </c>
-      <c r="D40" s="14" t="s">
+      <c r="D43" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="E40" s="14" t="s">
+      <c r="E43" s="12" t="s">
         <v>82</v>
       </c>
-      <c r="F40" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="G40" s="14" t="s">
+      <c r="F43" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="G43" s="12" t="s">
         <v>83</v>
       </c>
-      <c r="I40" s="7"/>
-      <c r="J40" s="12"/>
-      <c r="K40" s="7"/>
-      <c r="L40" s="7"/>
-      <c r="M40" s="7"/>
-      <c r="N40" s="7"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="13"/>
-      <c r="B41" s="14" t="s">
+    </row>
+    <row r="44" spans="1:12" ht="26.25" customHeight="1">
+      <c r="B44" s="12" t="s">
         <v>68</v>
       </c>
-      <c r="C41" s="4" t="s">
+      <c r="C44" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="D41" s="4" t="s">
+      <c r="D44" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="E41" s="4" t="s">
+      <c r="E44" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="F41" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="G41" s="7" t="s">
+      <c r="F44" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="G44" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="I41" s="7"/>
-      <c r="J41" s="12"/>
-      <c r="K41" s="7"/>
-      <c r="L41" s="7"/>
-      <c r="M41" s="7"/>
-      <c r="N41" s="7"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="13"/>
-      <c r="B42" s="14" t="s">
+    </row>
+    <row r="45" spans="1:12" ht="27.75" customHeight="1">
+      <c r="B45" s="12" t="s">
         <v>68</v>
       </c>
-      <c r="C42" s="4" t="s">
+      <c r="C45" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="D42" s="4" t="s">
+      <c r="D45" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="E42" s="4" t="s">
+      <c r="E45" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="F42" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="G42" s="7" t="s">
+      <c r="F45" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="G45" s="6" t="s">
         <v>88</v>
       </c>
-      <c r="I42" s="7"/>
-      <c r="J42" s="12"/>
-      <c r="K42" s="7"/>
-      <c r="L42" s="7"/>
-      <c r="M42" s="7"/>
-      <c r="N42" s="7"/>
-    </row>
-    <row r="43">
-      <c r="B43" s="16"/>
-      <c r="C43" s="17"/>
-      <c r="D43" s="17"/>
-      <c r="E43" s="17"/>
-      <c r="F43" s="17"/>
-      <c r="G43" s="17"/>
-    </row>
-    <row r="44">
-      <c r="B44" s="12"/>
-      <c r="C44" s="7"/>
-      <c r="D44" s="7"/>
-      <c r="E44" s="7"/>
-      <c r="F44" s="7"/>
-      <c r="G44" s="7"/>
-    </row>
-    <row r="46">
-      <c r="B46" s="1" t="s">
+    </row>
+    <row r="46" spans="1:12" ht="24" customHeight="1">
+      <c r="B46" s="27" t="s">
+        <v>68</v>
+      </c>
+      <c r="C46" s="27" t="s">
+        <v>8</v>
+      </c>
+      <c r="D46" s="27" t="s">
+        <v>9</v>
+      </c>
+      <c r="E46" s="28" t="s">
+        <v>104</v>
+      </c>
+      <c r="F46" s="13" t="s">
+        <v>53</v>
+      </c>
+      <c r="G46" s="27" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="47" spans="1:12" ht="26.4">
+      <c r="B47" s="27" t="s">
+        <v>68</v>
+      </c>
+      <c r="C47" s="27" t="s">
+        <v>102</v>
+      </c>
+      <c r="D47" s="27" t="s">
+        <v>98</v>
+      </c>
+      <c r="E47" s="28" t="s">
+        <v>103</v>
+      </c>
+      <c r="F47" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="G47" s="27" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="48" spans="1:12" ht="24" customHeight="1">
+      <c r="B48" s="22" t="s">
+        <v>68</v>
+      </c>
+      <c r="C48" s="22" t="s">
+        <v>105</v>
+      </c>
+      <c r="D48" s="22" t="s">
+        <v>106</v>
+      </c>
+      <c r="E48" s="31" t="s">
+        <v>107</v>
+      </c>
+      <c r="F48" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="G48" s="24" t="s">
+        <v>108</v>
+      </c>
+      <c r="L48" s="30"/>
+    </row>
+    <row r="49" spans="2:8" ht="13.2"/>
+    <row r="50" spans="2:8" ht="13.2"/>
+    <row r="51" spans="2:8" ht="13.2"/>
+    <row r="52" spans="2:8" ht="13.8">
+      <c r="B52" s="34" t="s">
         <v>89</v>
       </c>
-    </row>
-    <row r="47">
-      <c r="B47" s="2" t="s">
+      <c r="C52" s="35"/>
+      <c r="D52" s="35"/>
+      <c r="E52" s="35"/>
+      <c r="F52" s="35"/>
+      <c r="G52" s="35"/>
+    </row>
+    <row r="53" spans="2:8" ht="17.399999999999999">
+      <c r="B53" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C47" s="2" t="s">
+      <c r="C53" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D47" s="2" t="s">
+      <c r="D53" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E47" s="2" t="s">
+      <c r="E53" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F47" s="2" t="s">
+      <c r="F53" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G47" s="2" t="s">
+      <c r="G53" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="48">
-      <c r="B48" s="18" t="s">
+      <c r="H53" s="1" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="54" spans="2:8" ht="26.4">
+      <c r="B54" s="14" t="s">
         <v>89</v>
       </c>
-      <c r="C48" s="18" t="s">
+      <c r="C54" s="14" t="s">
         <v>90</v>
       </c>
-      <c r="D48" s="18" t="s">
+      <c r="D54" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="E48" s="18" t="s">
+      <c r="E54" s="14" t="s">
         <v>91</v>
       </c>
-      <c r="F48" s="18" t="s">
+      <c r="F54" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="G48" s="4" t="s">
+      <c r="G54" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="49">
-      <c r="B49" s="19" t="s">
+    <row r="55" spans="2:8" ht="13.2">
+      <c r="B55" s="15" t="s">
         <v>89</v>
       </c>
-      <c r="C49" s="19" t="s">
+      <c r="C55" s="15" t="s">
         <v>69</v>
       </c>
-      <c r="D49" s="19" t="s">
+      <c r="D55" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="E49" s="19" t="s">
+      <c r="E55" s="15" t="s">
         <v>92</v>
       </c>
-      <c r="F49" s="19" t="s">
+      <c r="F55" s="15" t="s">
         <v>53</v>
       </c>
-      <c r="G49" s="19" t="s">
+      <c r="G55" s="15" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="50">
-      <c r="B50" s="18" t="s">
+    <row r="56" spans="2:8" ht="26.4">
+      <c r="B56" s="14" t="s">
         <v>89</v>
       </c>
-      <c r="C50" s="18" t="s">
+      <c r="C56" s="14" t="s">
         <v>94</v>
       </c>
-      <c r="D50" s="18" t="s">
+      <c r="D56" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="E50" s="18" t="s">
+      <c r="E56" s="14" t="s">
         <v>95</v>
       </c>
-      <c r="F50" s="18" t="s">
+      <c r="F56" s="14" t="s">
         <v>53</v>
       </c>
-      <c r="G50" s="18" t="s">
+      <c r="G56" s="14" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="51">
-      <c r="B51" s="20"/>
-      <c r="C51" s="21"/>
-      <c r="D51" s="21"/>
-      <c r="E51" s="21"/>
-      <c r="F51" s="21"/>
-      <c r="G51" s="21"/>
-    </row>
-    <row r="52">
-      <c r="B52" s="22" t="s">
+    <row r="57" spans="2:8" ht="13.2"/>
+    <row r="58" spans="2:8" ht="13.2"/>
+    <row r="59" spans="2:8" ht="13.2"/>
+    <row r="60" spans="2:8" ht="13.2"/>
+    <row r="61" spans="2:8" ht="13.2"/>
+    <row r="62" spans="2:8" ht="13.2">
+      <c r="B62" s="36" t="s">
         <v>96</v>
       </c>
-    </row>
-    <row r="53">
-      <c r="B53" s="20"/>
-      <c r="C53" s="21"/>
-      <c r="D53" s="21"/>
-      <c r="E53" s="21"/>
-      <c r="F53" s="21"/>
-      <c r="G53" s="21"/>
-    </row>
-    <row r="54">
-      <c r="B54" s="23"/>
-      <c r="C54" s="24"/>
-      <c r="D54" s="24"/>
-      <c r="E54" s="24"/>
-      <c r="F54" s="24"/>
-      <c r="G54" s="24"/>
-    </row>
-    <row r="55">
-      <c r="B55" s="25"/>
-      <c r="C55" s="26"/>
-      <c r="D55" s="26"/>
-      <c r="E55" s="26"/>
-      <c r="F55" s="26"/>
-      <c r="G55" s="26"/>
-    </row>
-    <row r="56">
-      <c r="B56" s="23"/>
-      <c r="C56" s="24"/>
-      <c r="D56" s="24"/>
-      <c r="E56" s="24"/>
-      <c r="F56" s="24"/>
-      <c r="G56" s="24"/>
-    </row>
-    <row r="57">
-      <c r="B57" s="20"/>
-      <c r="C57" s="21"/>
-      <c r="D57" s="21"/>
-      <c r="E57" s="21"/>
-      <c r="F57" s="21"/>
-      <c r="G57" s="21"/>
-    </row>
-    <row r="58">
-      <c r="B58" s="20"/>
-      <c r="C58" s="21"/>
-      <c r="D58" s="21"/>
-      <c r="E58" s="21"/>
-      <c r="F58" s="21"/>
-      <c r="G58" s="21"/>
-    </row>
-    <row r="59">
-      <c r="B59" s="20"/>
-      <c r="C59" s="21"/>
-      <c r="D59" s="21"/>
-      <c r="E59" s="21"/>
-      <c r="F59" s="21"/>
-      <c r="G59" s="21"/>
-    </row>
-    <row r="60">
-      <c r="B60" s="20"/>
-      <c r="C60" s="21"/>
-      <c r="D60" s="21"/>
-      <c r="E60" s="21"/>
-      <c r="F60" s="21"/>
-      <c r="G60" s="21"/>
-    </row>
-    <row r="61">
-      <c r="B61" s="20"/>
-      <c r="C61" s="21"/>
-      <c r="D61" s="21"/>
-      <c r="E61" s="21"/>
-      <c r="F61" s="21"/>
-      <c r="G61" s="21"/>
-    </row>
-    <row r="62">
-      <c r="B62" s="20"/>
-      <c r="C62" s="21"/>
-      <c r="D62" s="21"/>
-      <c r="E62" s="21"/>
-      <c r="F62" s="21"/>
-      <c r="G62" s="21"/>
-    </row>
-    <row r="63">
-      <c r="B63" s="20"/>
-      <c r="C63" s="21"/>
-      <c r="D63" s="21"/>
-      <c r="E63" s="21"/>
-      <c r="F63" s="21"/>
-      <c r="G63" s="21"/>
-    </row>
-    <row r="64">
-      <c r="B64" s="20"/>
-      <c r="C64" s="21"/>
-      <c r="D64" s="21"/>
-      <c r="E64" s="21"/>
-      <c r="F64" s="21"/>
-      <c r="G64" s="21"/>
+      <c r="C62" s="35"/>
+      <c r="D62" s="35"/>
+      <c r="E62" s="35"/>
+      <c r="F62" s="35"/>
+      <c r="G62" s="35"/>
+    </row>
+    <row r="63" spans="2:8" ht="13.2">
+      <c r="B63" s="16"/>
+      <c r="C63" s="17"/>
+      <c r="D63" s="17"/>
+      <c r="E63" s="17"/>
+      <c r="F63" s="17"/>
+      <c r="G63" s="17"/>
+    </row>
+    <row r="64" spans="2:8" ht="13.2">
+      <c r="B64" s="18"/>
+      <c r="C64" s="19"/>
+      <c r="D64" s="19"/>
+      <c r="E64" s="19"/>
+      <c r="F64" s="19"/>
+      <c r="G64" s="19"/>
+    </row>
+    <row r="65" spans="2:14" ht="15.75" customHeight="1">
+      <c r="B65" s="20"/>
+      <c r="C65" s="21"/>
+      <c r="D65" s="21"/>
+      <c r="E65" s="21"/>
+      <c r="F65" s="21"/>
+      <c r="G65" s="21"/>
+    </row>
+    <row r="66" spans="2:14" ht="15.75" customHeight="1">
+      <c r="B66" s="18"/>
+      <c r="C66" s="19"/>
+      <c r="D66" s="19"/>
+      <c r="E66" s="19"/>
+      <c r="F66" s="19"/>
+      <c r="G66" s="19"/>
+    </row>
+    <row r="67" spans="2:14" ht="15.75" customHeight="1">
+      <c r="B67" s="16"/>
+      <c r="C67" s="16" t="s">
+        <v>111</v>
+      </c>
+      <c r="D67" s="17"/>
+      <c r="E67" s="17"/>
+      <c r="F67" s="17"/>
+      <c r="G67" s="17"/>
+    </row>
+    <row r="69" spans="2:14" ht="15.75" customHeight="1">
+      <c r="I69" s="6"/>
+      <c r="J69" s="6"/>
+      <c r="K69" s="6"/>
+      <c r="L69" s="6"/>
+      <c r="M69" s="6"/>
+      <c r="N69" s="6"/>
+    </row>
+    <row r="70" spans="2:14" ht="15.75" customHeight="1">
+      <c r="I70" s="6"/>
+      <c r="J70" s="10"/>
+      <c r="K70" s="6"/>
+      <c r="L70" s="6"/>
+      <c r="M70" s="6"/>
+      <c r="N70" s="6"/>
+    </row>
+    <row r="71" spans="2:14" ht="15.75" customHeight="1">
+      <c r="I71" s="6"/>
+      <c r="J71" s="10"/>
+      <c r="K71" s="6"/>
+      <c r="L71" s="6"/>
+      <c r="M71" s="6"/>
+      <c r="N71" s="6"/>
+    </row>
+    <row r="72" spans="2:14" ht="15.75" customHeight="1">
+      <c r="I72" s="6"/>
+      <c r="J72" s="10"/>
+      <c r="K72" s="6"/>
+      <c r="L72" s="6"/>
+      <c r="M72" s="6"/>
+      <c r="N72" s="6"/>
+    </row>
+    <row r="73" spans="2:14" ht="15.75" customHeight="1">
+      <c r="I73" s="6"/>
+      <c r="J73" s="10"/>
+      <c r="K73" s="6"/>
+      <c r="L73" s="6"/>
+      <c r="M73" s="6"/>
+      <c r="N73" s="6"/>
+    </row>
+    <row r="74" spans="2:14" ht="15.75" customHeight="1">
+      <c r="I74" s="6"/>
+      <c r="J74" s="10"/>
+      <c r="K74" s="6"/>
+      <c r="L74" s="6"/>
+      <c r="M74" s="6"/>
+      <c r="N74" s="6"/>
+    </row>
+    <row r="75" spans="2:14" ht="15.75" customHeight="1">
+      <c r="I75" s="6"/>
+      <c r="J75" s="10"/>
+      <c r="K75" s="6"/>
+      <c r="L75" s="6"/>
+      <c r="M75" s="6"/>
+      <c r="N75" s="6"/>
+    </row>
+    <row r="76" spans="2:14" ht="15.75" customHeight="1">
+      <c r="I76" s="6"/>
+      <c r="J76" s="10"/>
+      <c r="K76" s="6"/>
+      <c r="L76" s="6"/>
+      <c r="M76" s="6"/>
+      <c r="N76" s="6"/>
+    </row>
+    <row r="77" spans="2:14" ht="15.75" customHeight="1">
+      <c r="I77" s="6"/>
+      <c r="J77" s="10"/>
+      <c r="K77" s="6"/>
+      <c r="L77" s="6"/>
+      <c r="M77" s="6"/>
+      <c r="N77" s="6"/>
+    </row>
+    <row r="79" spans="2:14" ht="15.75" customHeight="1">
+      <c r="B79" s="10"/>
+      <c r="C79" s="6"/>
+      <c r="D79" s="6"/>
+      <c r="E79" s="6"/>
+      <c r="F79" s="6"/>
+      <c r="G79" s="6"/>
     </row>
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="B2:G2"/>
-    <mergeCell ref="B23:G23"/>
-    <mergeCell ref="B33:G33"/>
-    <mergeCell ref="B46:G46"/>
+    <mergeCell ref="B24:G24"/>
+    <mergeCell ref="B36:G36"/>
     <mergeCell ref="B52:G52"/>
+    <mergeCell ref="B62:G62"/>
   </mergeCells>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <tableParts count="5">
-    <tablePart r:id="rId7"/>
-    <tablePart r:id="rId8"/>
-    <tablePart r:id="rId9"/>
-    <tablePart r:id="rId10"/>
-    <tablePart r:id="rId11"/>
+    <tablePart r:id="rId2"/>
+    <tablePart r:id="rId3"/>
+    <tablePart r:id="rId4"/>
+    <tablePart r:id="rId5"/>
+    <tablePart r:id="rId6"/>
   </tableParts>
 </worksheet>
 </file>